--- a/Security Deposit.xlsx
+++ b/Security Deposit.xlsx
@@ -1,50 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28523"/>
+  <x:workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MCT\RealEstate\RealEstate Dev\BlueRidge-Real-Estate\Property-Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\BcCore\Platform\Server\Prod.Ncl\Runtime\Office\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB2932B-64E1-42C5-9A95-C99EE9183D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="TranslationData" sheetId="2" r:id="rId2"/>
-    <sheet name="CaptionData" sheetId="3" r:id="rId3"/>
-    <sheet name="Aggregated Metadata" sheetId="4" r:id="rId4"/>
-  </sheets>
-  <definedNames>
-    <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</definedName>
-    <definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</definedName>
-    <definedName name="ReportMetadata.ExtensionID" comment="Use this function to get the Extension ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</definedName>
-    <definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</definedName>
-    <definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</definedName>
-    <definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</definedName>
-    <definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</definedName>
-    <definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</definedName>
-    <definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</definedName>
-    <definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</definedName>
-    <definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</definedName>
-    <definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</definedName>
-    <definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</definedName>
-    <definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</definedName>
-    <definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</definedName>
-    <definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</definedName>
-    <definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</definedName>
-    <definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</definedName>
-    <definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</definedName>
-  </definedNames>
-  <calcPr calcId="0"/>
-</workbook>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C047C7D7-11EE-4DA8-AAC2-1AF211845798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <x:bookViews>
+    <x:workbookView xWindow="-71110" yWindow="3060" windowWidth="28800" windowHeight="15320" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="Data" sheetId="1" r:id="rId1"/>
+    <x:sheet name="TranslationData" sheetId="2" r:id="rId2"/>
+    <x:sheet name="CaptionData" sheetId="3" r:id="rId3"/>
+    <x:sheet name="Aggregated Metadata" sheetId="4" r:id="rId4"/>
+  </x:sheets>
+  <x:definedNames>
+    <x:definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionID" comment="Use this function to get the Extension ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.CompanyDisplayName" comment="Use this function to get the Company display name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company display name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.LayoutName" comment="Use this function to get the Layout name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Layout name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.LayoutCaption" comment="Use this function to get the Layout caption from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Layout caption",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+    <x:definedName name="ReportRequest.LayoutId" comment="Use this function to get the Layout id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Layout id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none",)</x:definedName>
+  </x:definedNames>
+  <x:calcPr calcId="191029"/>
+  <x:extLst>
+    <x:ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </x:ext>
+  </x:extLst>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="60">
+  <si>
+    <t>TemplateColumn</t>
+  </si>
   <si>
     <t>Language</t>
   </si>
@@ -58,6 +78,9 @@
     <t>Caption</t>
   </si>
   <si>
+    <t>KeyValue</t>
+  </si>
+  <si>
     <t>Request Page Option</t>
   </si>
   <si>
@@ -196,258 +219,245 @@
     <t>Tenant Entra Id Value</t>
   </si>
   <si>
-    <t>CustomDateRange</t>
-  </si>
-  <si>
-    <t>Contract_ID</t>
-  </si>
-  <si>
-    <t>Customer_Name</t>
-  </si>
-  <si>
-    <t>Property_Name</t>
-  </si>
-  <si>
-    <t>Unit_Name</t>
-  </si>
-  <si>
-    <t>Contract_Start_Date</t>
-  </si>
-  <si>
-    <t>Contract_End_Date</t>
-  </si>
-  <si>
-    <t>Opening_Balance</t>
-  </si>
-  <si>
-    <t>Additions</t>
-  </si>
-  <si>
-    <t>CarriedForwardOut</t>
-  </si>
-  <si>
-    <t>Refund</t>
-  </si>
-  <si>
-    <t>Closing_Balance</t>
-  </si>
-  <si>
-    <t/>
+    <t>Company display name</t>
+  </si>
+  <si>
+    <t>Company display name Value</t>
+  </si>
+  <si>
+    <t>Layout name</t>
+  </si>
+  <si>
+    <t>Layout name Value</t>
+  </si>
+  <si>
+    <t>Layout caption</t>
+  </si>
+  <si>
+    <t>Layout caption Value</t>
+  </si>
+  <si>
+    <t>Layout id</t>
+  </si>
+  <si>
+    <t>Layout id Value</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="3">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0C0C0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC0C0C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC0C0C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC0C0C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC0C0C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFC0C0C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2 xr">
+  <x:numFmts count="0"/>
+  <x:fonts count="2" x14ac:knownFonts="1">
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="3">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC0C0C0"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+  </x:fills>
+  <x:borders count="1">
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="5">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <x:xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </x:cellStyles>
+  <x:dxfs count="5">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:i val="0"/>
+        <x:strike val="0"/>
+        <x:condense val="0"/>
+        <x:extend val="0"/>
+        <x:outline val="0"/>
+        <x:shadow val="0"/>
+        <x:u val="none"/>
+        <x:vertAlign val="baseline"/>
+        <x:sz val="11"/>
+        <x:color auto="1"/>
+        <x:name val="Calibri"/>
+        <x:family val="2"/>
+        <x:scheme val="minor"/>
+      </x:font>
+      <x:numFmt numFmtId="30" formatCode="@"/>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor indexed="64"/>
+          <x:bgColor rgb="FFC0C0C0"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:i val="0"/>
+        <x:strike val="0"/>
+        <x:condense val="0"/>
+        <x:extend val="0"/>
+        <x:outline val="0"/>
+        <x:shadow val="0"/>
+        <x:u val="none"/>
+        <x:vertAlign val="baseline"/>
+        <x:sz val="11"/>
+        <x:color auto="1"/>
+        <x:name val="Calibri"/>
+        <x:family val="2"/>
+        <x:scheme val="minor"/>
+      </x:font>
+      <x:numFmt numFmtId="30" formatCode="@"/>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor indexed="64"/>
+          <x:bgColor rgb="FFC0C0C0"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:i val="0"/>
+        <x:strike val="0"/>
+        <x:condense val="0"/>
+        <x:extend val="0"/>
+        <x:outline val="0"/>
+        <x:shadow val="0"/>
+        <x:u val="none"/>
+        <x:vertAlign val="baseline"/>
+        <x:sz val="11"/>
+        <x:color auto="1"/>
+        <x:name val="Calibri"/>
+        <x:family val="2"/>
+        <x:scheme val="minor"/>
+      </x:font>
+      <x:numFmt numFmtId="30" formatCode="@"/>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor indexed="64"/>
+          <x:bgColor rgb="FFC0C0C0"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:i val="0"/>
+        <x:strike val="0"/>
+        <x:condense val="0"/>
+        <x:extend val="0"/>
+        <x:outline val="0"/>
+        <x:shadow val="0"/>
+        <x:u val="none"/>
+        <x:vertAlign val="baseline"/>
+        <x:sz val="11"/>
+        <x:color auto="1"/>
+        <x:name val="Calibri"/>
+        <x:family val="2"/>
+        <x:scheme val="minor"/>
+      </x:font>
+      <x:numFmt numFmtId="30" formatCode="@"/>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor indexed="64"/>
+          <x:bgColor rgb="FFC0C0C0"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:i val="0"/>
+        <x:strike val="0"/>
+        <x:condense val="0"/>
+        <x:extend val="0"/>
+        <x:outline val="0"/>
+        <x:shadow val="0"/>
+        <x:u val="none"/>
+        <x:vertAlign val="baseline"/>
+        <x:sz val="11"/>
+        <x:color auto="1"/>
+        <x:name val="Calibri"/>
+        <x:family val="2"/>
+        <x:scheme val="minor"/>
+      </x:font>
+      <x:numFmt numFmtId="30" formatCode="@"/>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor indexed="64"/>
+          <x:bgColor rgb="FFC0C0C0"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
+  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+    </x:ext>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
+    </x:ext>
+  </x:extLst>
+</x:styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" name="Data" displayName="Data" ref="A1:L2" totalsRowShown="0" headerRowDxfId="4">
-  <autoFilter ref="A1:L2" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="CustomDateRange"/>
-    <tableColumn id="2" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Contract_ID"/>
-    <tableColumn id="3" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Customer_Name"/>
-    <tableColumn id="4" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Property_Name"/>
-    <tableColumn id="5" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Unit_Name"/>
-    <tableColumn id="6" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Contract_Start_Date"/>
-    <tableColumn id="7" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Contract_End_Date"/>
-    <tableColumn id="8" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Opening_Balance"/>
-    <tableColumn id="9" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Additions"/>
-    <tableColumn id="10" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="CarriedForwardOut"/>
-    <tableColumn id="11" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Refund"/>
-    <tableColumn id="12" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}" name="Closing_Balance"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Data" displayName="Data" ref="A1:M2" totalsRowShown="0" headerRowDxfId="4" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:M2" xr:uid="{41D726F2-778D-4B1C-A5EA-875FED73D050}"/>
+  <x:tableColumns count="13">
+    <x:tableColumn id="1" name="CustomDateRange" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="2" name="Contract_ID" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="3" name="Customer_Name" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="4" name="Property_Name" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="5" name="Unit_Name" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="6" name="Contract_Start_Date" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="7" name="Contract_End_Date" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="8" name="Opening_Balance" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="9" name="Additions" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="10" name="CarriedForwardIn" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="11" name="CarriedForwardOut" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="12" name="Refund" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+    <x:tableColumn id="13" name="Closing_Balance" xr3:uid="{21867904-D69E-41E3-B5BE-D9B124B8D7E4}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -474,8 +484,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{134EB915-8B19-4838-BDED-CECBACACF4F9}" name="ReportMetadataValues" displayName="ReportMetadataValues" ref="A1:B23" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A1:B23" xr:uid="{134EB915-8B19-4838-BDED-CECBACACF4F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{134EB915-8B19-4838-BDED-CECBACACF4F9}" name="ReportMetadataValues" displayName="ReportMetadataValues" ref="A1:B10" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A1:B10" xr:uid="{134EB915-8B19-4838-BDED-CECBACACF4F9}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{5CBC1C08-5A8D-42BB-92CA-C3F1D0EF0A4D}" name="Report Property"/>
     <tableColumn id="2" xr3:uid="{920E2177-8B70-4968-B161-4C2CF0A824C6}" name="Report Property Value"/>
@@ -485,8 +495,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1DFF5EE2-2A86-40DE-9DFD-1E96553323F6}" name="ReportRequestValues" displayName="ReportRequestValues" ref="D1:E23" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="D1:E23" xr:uid="{1DFF5EE2-2A86-40DE-9DFD-1E96553323F6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1DFF5EE2-2A86-40DE-9DFD-1E96553323F6}" name="ReportRequestValues" displayName="ReportRequestValues" ref="D1:E15" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="D1:E15" xr:uid="{1DFF5EE2-2A86-40DE-9DFD-1E96553323F6}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{E6EF2D44-8AB2-42E8-A7E3-9B148922AA59}" name="Request Property"/>
     <tableColumn id="2" xr3:uid="{FA31CE16-2D0E-4E4D-BC19-2B03E00E4B08}" name="Request Property Value"/>
@@ -518,9 +528,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -558,7 +568,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -664,7 +674,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -806,94 +816,128 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
+  <x:dimension ref="A1:A2"/>
+  <x:sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18.3828125" bestFit="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row>
+      <x:c r="A1" t="str">
+        <x:v>CustomDateRange</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Contract_ID</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>Customer_Name</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>Property_Name</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>Unit_Name</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>Contract_Start_Date</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>Contract_End_Date</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>Opening_Balance</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>Additions</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>CarriedForwardIn</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>CarriedForwardOut</x:v>
+      </x:c>
+      <x:c r="L1" t="str">
+        <x:v>Refund</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>Closing_Balance</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c r="A2" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="B2" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v/>
+      </x:c>
+      <x:c r="F2" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H2" s="4" t="n">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="I2" s="4" t="n">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="J2" s="4" t="n">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="K2" s="4" t="n">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="L2" s="4" t="n">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="M2" s="4" t="n">
+        <x:v>0.0</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart r:id="rId1"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B660A3C-AF79-49CD-9630-9BBF64CB79D9}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -904,24 +948,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B660A3C-AF79-49CD-9630-9BBF64CB79D9}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAFD9D77-FE1A-4986-8555-546CEA41E376}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -932,185 +981,152 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAFD9D77-FE1A-4986-8555-546CEA41E376}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63D37DBB-4AC2-46F2-B64A-5C237CE209EB}">
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" customWidth="1"/>
+    <col min="1" max="1" width="25.69140625" customWidth="1"/>
+    <col min="2" max="2" width="40.69140625" customWidth="1"/>
+    <col min="3" max="3" width="5.69140625" customWidth="1"/>
+    <col min="4" max="4" width="25.69140625" customWidth="1"/>
+    <col min="5" max="5" width="40.69140625" customWidth="1"/>
+    <col min="6" max="6" width="5.69140625" customWidth="1"/>
+    <col min="7" max="7" width="25.69140625" customWidth="1"/>
+    <col min="8" max="8" width="40.69140625" customWidth="1"/>
+    <col min="9" max="9" width="5.69140625" customWidth="1"/>
+    <col min="10" max="10" width="40.69140625" customWidth="1"/>
+    <col min="11" max="11" width="25.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" t="s">
         <v>47</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63D37DBB-4AC2-46F2-B64A-5C237CE209EB}">
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="25.6640625" customWidth="1"/>
-    <col min="2" max="2" width="40.6640625" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" customWidth="1"/>
-    <col min="5" max="5" width="40.6640625" customWidth="1"/>
-    <col min="6" max="6" width="5.6640625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="40.6640625" customWidth="1"/>
-    <col min="9" max="9" width="5.6640625" customWidth="1"/>
-    <col min="10" max="10" width="40.6640625" customWidth="1"/>
-    <col min="11" max="11" width="25.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="K2" t="s">
         <v>48</v>
       </c>
-      <c r="E2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
         <v>38</v>
@@ -1119,12 +1135,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
         <v>40</v>
@@ -1133,26 +1149,58 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="D11" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
